--- a/Lab_4/data/partB/param_optimization_process/v200_k10_s100_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v200_k10_s100_results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" t="n">
         <v>5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
       </c>
       <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -573,16 +573,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -594,7 +594,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -686,10 +686,10 @@
         <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -698,22 +698,22 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>4</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -726,49 +726,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
         <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>28</v>
-      </c>
-      <c r="G6" t="n">
-        <v>17</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -790,31 +790,31 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -842,37 +842,37 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -900,10 +900,10 @@
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -912,19 +912,19 @@
         <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
         <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,34 +998,34 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1044,10 +1044,10 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1062,22 +1062,22 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1126,7 +1126,7 @@
         <v>62</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -1154,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
         <v>8</v>
@@ -1163,28 +1163,28 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1200,10 +1200,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,31 +1246,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1279,16 +1279,16 @@
         <v>3</v>
       </c>
       <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
         <v>2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11909,7 +11909,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13218,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14323,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17587,7 +17587,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17655,7 +17655,7 @@
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18539,7 +18539,7 @@
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20188,7 +20188,7 @@
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20936,7 @@
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22228,7 +22228,7 @@
       </c>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22636,7 +22636,7 @@
       </c>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22738,7 +22738,7 @@
       </c>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22755,7 +22755,7 @@
       </c>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22874,7 +22874,7 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22925,7 +22925,7 @@
       </c>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24149,7 +24149,7 @@
       </c>
       <c r="C1344" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="C1356" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24489,7 +24489,7 @@
       </c>
       <c r="C1364" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24506,7 +24506,7 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24523,7 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24608,7 +24608,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24897,7 +24897,7 @@
       </c>
       <c r="C1388" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25220,7 +25220,7 @@
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26223,7 +26223,7 @@
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26308,7 +26308,7 @@
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
